--- a/web/public/templates/vendors_template.xlsx
+++ b/web/public/templates/vendors_template.xlsx
@@ -445,19 +445,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>company_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -473,6 +474,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>contact_email</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>remarks</t>
         </is>
       </c>
     </row>
@@ -488,12 +494,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,7 +522,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>company_name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,7 +532,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vendor / company name.</t>
+          <t>Company name. Must be unique — an existing name is rejected rather than creating a second, indistinguishable vendor.</t>
         </is>
       </c>
     </row>
@@ -577,7 +583,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vendor email address.</t>
+          <t>Vendor email address. Optional, but must be valid and unique when given.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Free-text note about this vendor. Not used in any business rule; up to 2000 characters.</t>
         </is>
       </c>
     </row>

--- a/web/public/templates/vendors_template.xlsx
+++ b/web/public/templates/vendors_template.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/web/public/templates/vendors_template.xlsx
+++ b/web/public/templates/vendors_template.xlsx
@@ -458,27 +458,27 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>company_name</t>
+          <t>COMPANY_NAME</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>CONTACT_PERSON</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>CONTACT_PHONE</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>CONTACT_EMAIL</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>remarks</t>
+          <t>REMARKS</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>company_name</t>
+          <t>COMPANY_NAME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>CONTACT_PERSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>CONTACT_PHONE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>CONTACT_EMAIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>remarks</t>
+          <t>REMARKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/web/public/templates/vendors_template.xlsx
+++ b/web/public/templates/vendors_template.xlsx
@@ -73,10 +73,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -494,117 +497,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Column names are matched on SPELLING ONLY. Upper or lower case makes no difference, and spaces, hyphens and underscores are treated the same - so CUST_CD, Cust_CD and "cust cd" are the same column. The headers on the Data sheet are all-caps; keep the wording, and the case is up to you. A sheet filled in with Caps Lock on uploads exactly like any other. Do not rename, reorder or delete columns - only the wording identifies them.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
           <t>COMPANY_NAME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Company name. Must be unique — an existing name is rejected rather than creating a second, indistinguishable vendor.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CONTACT_PERSON</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Primary contact person.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CONTACT_PHONE</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Contact phone number.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CONTACT_EMAIL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Vendor email address. Optional, but must be valid and unique when given.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Free-text note about this vendor. Not used in any business rule; up to 2000 characters.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>